--- a/02_DIA_inicio_2026_analisis_assets/rbd_9709_escuela-blue-star-college_nt1_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9709_escuela-blue-star-college_nt1_rubricas.xlsx
@@ -1992,13 +1992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B222608A-6ECC-4695-8654-40CA8E32FBAB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{482827F0-FE70-4E95-B98A-C65967D6636A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D046A9EE-E646-4B10-946B-2FC4BF338676}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{CC331645-56E0-49BA-8308-AA7AB4BB0034}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FBEF37DA-C161-46E3-ABEA-13AE3147711C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{100C6EF7-2A3E-471B-925C-ABF3DAD07646}"/>
 </file>